--- a/samples/interlock_sample.xlsx
+++ b/samples/interlock_sample.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,389 +425,360 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>guide_type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>equipment_model</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>interlock_code</t>
-        </is>
-      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>interlock_name</t>
+          <t>code</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>action_method</t>
+          <t>title</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>equipment_name</t>
+          <t>process_area</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>summary</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>step1_title</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>interlock_description</t>
+          <t>step1_description</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>step1_question</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>step1_normal_result</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>trigger_condition</t>
+          <t>step1_caution</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>cause</t>
+          <t>step2_title</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>check_points</t>
+          <t>step2_description</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>action_steps</t>
+          <t>step2_question</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>reset_condition</t>
+          <t>step2_normal_result</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>caution</t>
+          <t>step2_caution</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>related_parts</t>
+          <t>step3_title</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>owner_team</t>
+          <t>step3_description</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>approval_required</t>
+          <t>step3_question</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>step3_normal_result</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>step3_caution</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>INTERLOCK</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Mirra</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>ILK-5001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>EMO Activated</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>위험 요소를 제거하고 안전을 확인한 후 EMO를 해제하고 정상 절차로 복귀한다</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CMP Polisher #1</t>
+          <t>CMP</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CMP</t>
+          <t>비상정지(EMO) 작동 시 조치 가이드</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>FAB2-A</t>
+          <t>설비 주변 안전 확인</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>비상정지로 설비 전체 정지</t>
+          <t>설비 주변 인원 및 이상 상태를 확인한다</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>설비 주변이 안전한 상태인가요?</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>안전 확인됨. 눌린 EMO 버튼을 확인하세요.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>EMO 버튼 눌림</t>
+          <t>모든 위험요소 제거 후 진행</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>작업자 조작/안전회로 단선</t>
+          <t>EMO 버튼 복귀</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>눌린 EMO 위치/안전회로 확인</t>
+          <t>눌린 EMO 버튼을 복귀하고 안전회로 정상을 확인한다</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1. 주변 확인 2. EMO 복귀 3. 재기동</t>
+          <t>안전회로가 정상 복귀되었나요?</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>모든 위험요소 제거 후 리셋</t>
+          <t>정상 복귀. 규정 절차에 따라 재기동하세요.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>안전 확인 후에만 리셋</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>EMO Button;Safety Relay</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>안전팀</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>emo;safety</t>
-        </is>
-      </c>
+          <t>안전 담당자 확인 필수</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ebara</t>
+          <t>INTERLOCK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ILK-5002</t>
+          <t>LKP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Slurry Leak Detected</t>
+          <t>ILK-5004</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>누액 원인을 제거하고 세정 건조 후 인터락을 해제한다</t>
+          <t>DIW Supply Fail</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CMP Polisher #2</t>
+          <t>Clean</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CMP</t>
+          <t>DIW 공급 실패 인터락 발생 시 조치 가이드</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FAB2-B</t>
+          <t>DIW 공급 압력 확인</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>슬러리 누액 감지로 공급 차단</t>
+          <t>DIW 공급 압력을 확인한다</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>공급 압력이 정상 범위인가요?</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Chemical</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>누액 센서 트립</t>
-        </is>
-      </c>
+          <t>압력 정상. 밸브 개도를 확인하세요.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>라인 누액/드레인 막힘</t>
+          <t>밸브 및 라인 점검</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>누액 위치/라인 상태 확인</t>
+          <t>공급 밸브 개도와 라인 상태를 점검하고 정상화한다</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1. 격리 2. 조임 또는 교체 3. 세정 건조</t>
+          <t>공급이 정상화되었나요?</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>누액 완전 제거 후 리셋</t>
+          <t>정상화 확인. 조치 완료.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>보호구 착용</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Leak Sensor;Slurry Fitting</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>CMP설비팀</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>leak;slurry</t>
-        </is>
-      </c>
+          <t>건식 세정 진행 금지</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>INTERLOCK</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>LK</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ILK-5003</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>DOOR_OPEN_INT</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Door Open Interlock</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>도어를 완전히 닫고 스위치 정상 동작 확인 후 해제한다</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CMP Polisher #3</t>
+          <t>CMP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CMP</t>
+          <t>도어 개방 인터락 발생 시 조치 가이드</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>FAB3-A</t>
+          <t>Door Sensor 상태 확인</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>메인 도어 개방으로 구동 금지</t>
+          <t>Door sensor LED 상태를 확인한다</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>Sensor LED가 정상 점등 상태인가요?</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>정상으로 판단되어 추가 조치가 필요하지 않습니다.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>도어 미폐쇄</t>
+          <t>Door 개방 시 안전 유의</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>도어 스위치 접점 불량</t>
+          <t>Door 폐쇄 및 리셋</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>도어 폐쇄/스위치 접점 확인</t>
+          <t>내부 잔류 확인 후 도어를 완전히 닫고 리셋한다</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1. 내부 확인 2. 도어 폐쇄 3. 리셋</t>
+          <t>도어 스위치 신호가 정상인가요?</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>내부 인원 확인 후 폐쇄</t>
+          <t>정상 확인. 조치 완료.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -815,26 +786,11 @@
           <t>내부 안전 확인 필수</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Door Switch</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>안전팀</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>door;safety</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/interlock_sample.xlsx
+++ b/samples/interlock_sample.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,77 +461,27 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>step1_title</t>
+          <t>step1_description</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>step1_description</t>
+          <t>step2_description</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>step1_question</t>
+          <t>step3_description</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>step1_normal_result</t>
+          <t>step4_description</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>step1_caution</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>step2_title</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>step2_description</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>step2_question</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>step2_normal_result</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>step2_caution</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>step3_title</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>step3_description</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>step3_question</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>step3_normal_result</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>step3_caution</t>
+          <t>step5_description</t>
         </is>
       </c>
     </row>
@@ -568,59 +518,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>설비 주변 안전 확인</t>
+          <t>설비 주변 인원 및 이상 상태를 확인한다. (모든 위험요소 제거 후 진행)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>설비 주변 인원 및 이상 상태를 확인한다</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>설비 주변이 안전한 상태인가요?</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>안전 확인됨. 눌린 EMO 버튼을 확인하세요.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>모든 위험요소 제거 후 진행</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>EMO 버튼 복귀</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>눌린 EMO 버튼을 복귀하고 안전회로 정상을 확인한다</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>안전회로가 정상 복귀되었나요?</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>정상 복귀. 규정 절차에 따라 재기동하세요.</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>안전 담당자 확인 필수</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+          <t>눌린 EMO 버튼을 복귀하고 안전회로 정상을 확인 후 규정 절차로 재기동한다. (안전 담당자 확인 필수)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -655,55 +563,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DIW 공급 압력 확인</t>
+          <t>DIW 공급 압력을 확인한다</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DIW 공급 압력을 확인한다</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>공급 압력이 정상 범위인가요?</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>압력 정상. 밸브 개도를 확인하세요.</t>
-        </is>
-      </c>
+          <t>공급 밸브 개도와 라인 상태를 점검하고 정상화한다. (건식 세정 진행 금지)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>밸브 및 라인 점검</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>공급 밸브 개도와 라인 상태를 점검하고 정상화한다</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>공급이 정상화되었나요?</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>정상화 확인. 조치 완료.</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>건식 세정 진행 금지</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -738,59 +608,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Door Sensor 상태 확인</t>
+          <t>Door sensor LED 상태를 확인한다. (Door 개방 시 안전 유의)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Door sensor LED 상태를 확인한다</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Sensor LED가 정상 점등 상태인가요?</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>정상으로 판단되어 추가 조치가 필요하지 않습니다.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Door 개방 시 안전 유의</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Door 폐쇄 및 리셋</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>내부 잔류 확인 후 도어를 완전히 닫고 리셋한다</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>도어 스위치 신호가 정상인가요?</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>정상 확인. 조치 완료.</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>내부 안전 확인 필수</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+          <t>내부 잔류 확인 후 도어를 완전히 닫고 리셋한다. (내부 안전 확인 필수)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
